--- a/SGC-CKN/Excel/af7482eb-2e31-444c-91e2-9435d815e6fa_Thi_công_cọc_khoan_nhồi_P1-121_D800_04-04-2026.xlsx
+++ b/SGC-CKN/Excel/af7482eb-2e31-444c-91e2-9435d815e6fa_Thi_công_cọc_khoan_nhồi_P1-121_D800_04-04-2026.xlsx
@@ -109,7 +109,7 @@
     <t>2</t>
   </si>
   <si>
-    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen, xám trắng, xám xanh TT dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">08:45
@@ -119,7 +119,7 @@
     <t>3</t>
   </si>
   <si>
-    <t>Cát pha xám ghi, xám nâu TT dẻo</t>
+    <t>Cát pha, xám ghi, xám nâu, xám vàng, TT dẻo</t>
   </si>
   <si>
     <t xml:space="preserve">09:10
@@ -139,7 +139,7 @@
     <t>5</t>
   </si>
   <si>
-    <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
+    <t>Sét xám vàng, nâu vàng, xám xanh, TT nửa cứng</t>
   </si>
   <si>
     <t xml:space="preserve">10:55
@@ -149,7 +149,7 @@
     <t>6</t>
   </si>
   <si>
-    <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
+    <t>Cát thô vừa, xám vàng, xám xanh, TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
     <t xml:space="preserve">11:35
@@ -159,7 +159,7 @@
     <t>7</t>
   </si>
   <si>
-    <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
+    <t>Cát thô, xám vàng, xám xanh, xám nâu, KC chặt</t>
   </si>
   <si>
     <t xml:space="preserve">14:30
@@ -169,7 +169,7 @@
     <t>8</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh, TT rất chặt</t>
+    <t>Sỏi xám vàng, nâu vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">17:20
